--- a/Day18-AI-Product-Finance-Model.xlsx
+++ b/Day18-AI-Product-Finance-Model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trung\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitHub\AI_20k\Day18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29E2B33-A246-4B35-9D95-1E12C642B83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEF3FE2-712C-4D06-9F33-5D6FDBA9953C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="16395" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="16395" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Assumptions" sheetId="1" r:id="rId1"/>
@@ -160,9 +160,6 @@
     <t>8. Decision Note  /  Ghi chú quyết định</t>
   </si>
   <si>
-    <t>Tại sao bạn chọn mức ARPU và CAC như trên? Logic gì để bảo vệ những con số này trước nhà đầu tư? Viết 2-3 câu...</t>
-  </si>
-  <si>
     <t>Tab 2 — UNIT ECONOMICS  /  Kinh tế đơn vị</t>
   </si>
   <si>
@@ -449,6 +446,9 @@
   </si>
   <si>
     <t>Chi phí API GPT-4o-mini dao động $360-$1,800/tháng cho 200 sv</t>
+  </si>
+  <si>
+    <t>Mức ARPU (100k-300k VNĐ) được định giá theo mô hình B2B cấp License cho nhà trường, neo trực tiếp vào bài toán tiết kiệm ~10.000 USD/năm ngân sách thuê TA, đồng thời thiết lập ranh giới an toàn để bù đắp chi phí gọi API LLM thường xuyên. Mức CAC (50k-200k VNĐ/khách) phản ánh đúng đặc thù chốt sales doanh nghiệp (cần demo, hội thảo, duyệt bảo mật); nhưng chi phí này thực chất đã được tối ưu quy mô vì mỗi hợp đồng B2B thành công sẽ tự động mang về hàng trăm user kích hoạt cùng một lúc.</t>
   </si>
 </sst>
 </file>
@@ -695,21 +695,6 @@
   </cellStyleXfs>
   <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -832,6 +817,21 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1277,495 +1277,495 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
     </row>
     <row r="3" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="8">
         <v>300000</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="8">
         <v>200000</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="8">
         <v>100000</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="10">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D8" s="10">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E8" s="10">
+        <v>2E-3</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B8" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="15">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="D8" s="15">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E8" s="15">
-        <v>2E-3</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="6" t="s">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8">
+        <v>60000</v>
+      </c>
+      <c r="D9" s="8">
+        <v>50000</v>
+      </c>
+      <c r="E9" s="8">
+        <v>40000</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B9" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="13">
-        <v>60000</v>
-      </c>
-      <c r="D9" s="13">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B11" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="8">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="8">
         <v>50000</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E12" s="8">
+        <v>100000</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="8">
+        <v>10000</v>
+      </c>
+      <c r="D13" s="8">
+        <v>20000</v>
+      </c>
+      <c r="E13" s="8">
         <v>40000</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B12" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="13">
-        <v>20000</v>
-      </c>
-      <c r="D12" s="13">
-        <v>50000</v>
-      </c>
-      <c r="E12" s="13">
-        <v>100000</v>
-      </c>
-      <c r="F12" s="14" t="s">
+      <c r="F13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B13" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="13">
+      <c r="G13" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D14" s="8">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="8">
         <v>10000</v>
       </c>
-      <c r="D13" s="13">
-        <v>20000</v>
-      </c>
-      <c r="E13" s="13">
-        <v>40000</v>
-      </c>
-      <c r="F13" s="14" t="s">
+      <c r="F14" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G14" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B14" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="13">
-        <v>2000</v>
-      </c>
-      <c r="D14" s="13">
-        <v>5000</v>
-      </c>
-      <c r="E14" s="13">
-        <v>10000</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="12">
         <f>C12+C13+C14</f>
         <v>32000</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="12">
         <f>D12+D13+D14</f>
         <v>75000</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="12">
         <f>E12+E13+E14</f>
         <v>150000</v>
       </c>
-      <c r="F15" s="18"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
     </row>
     <row r="18" spans="2:7" ht="23.25" x14ac:dyDescent="0.45">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="10">
         <v>0.01</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="10">
         <v>0.02</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="10">
         <v>0.05</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>127</v>
+      <c r="G18" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="15">
         <f>IFERROR(1/C18,0)</f>
         <v>100</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="15">
         <f>IFERROR(1/D18,0)</f>
         <v>50</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="15">
         <f>IFERROR(1/E18,0)</f>
         <v>20</v>
       </c>
-      <c r="F19" s="21"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
     </row>
     <row r="22" spans="2:7" ht="23.25" x14ac:dyDescent="0.45">
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="8">
         <v>50000</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="8">
         <v>100000</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="8">
         <v>200000</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>126</v>
+      <c r="G22" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="8">
         <v>80000000</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="8">
         <v>100000000</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="8">
         <v>120000000</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>133</v>
+      <c r="G25" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="8">
         <v>10000000</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="8">
         <v>15000000</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="8">
         <v>20000000</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="8">
         <v>15000000</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="8">
         <v>30000000</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="8">
         <v>40000000</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="17">
         <f>SUM(C25:C27)</f>
         <v>105000000</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="17">
         <f>SUM(D25:D27)</f>
         <v>145000000</v>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="17">
         <f>SUM(E25:E27)</f>
         <v>180000000</v>
       </c>
-      <c r="F28" s="21"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="8">
         <v>300000000</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="8">
         <v>300000000</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="8">
         <v>300000000</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2000000000</v>
+      </c>
+      <c r="D32" s="8">
+        <v>2000000000</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2000000000</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B32" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="13">
-        <v>2000000000</v>
-      </c>
-      <c r="D32" s="13">
-        <v>2000000000</v>
-      </c>
-      <c r="E32" s="13">
-        <v>2000000000</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="10">
         <v>0.2</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="10">
         <v>0.2</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="10">
         <v>0.2</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="18">
         <f>(1+C35)^(1/12)-1</f>
         <v>1.5309470499731193E-2</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="18">
         <f>(1+D35)^(1/12)-1</f>
         <v>1.5309470499731193E-2</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="18">
         <f>(1+E35)^(1/12)-1</f>
         <v>1.5309470499731193E-2</v>
       </c>
-      <c r="F36" s="21"/>
+      <c r="F36" s="16"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
     </row>
     <row r="39" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
+      <c r="B39" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
     </row>
     <row r="40" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
     </row>
     <row r="41" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B17:F17"/>
     <mergeCell ref="B39:F41"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B17:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1785,287 +1785,287 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+    </row>
+    <row r="3" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="11" t="s">
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B7" s="51" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B8" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="24">
+      <c r="C8" s="19">
         <f>'1. Assumptions'!C7</f>
         <v>300000</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="19">
         <f>'1. Assumptions'!D7</f>
         <v>200000</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="19">
         <f>'1. Assumptions'!E7</f>
         <v>100000</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B9" s="7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B9" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="24">
+      <c r="C9" s="19">
         <f>'1. Assumptions'!C15</f>
         <v>32000</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="19">
         <f>'1. Assumptions'!D15</f>
         <v>75000</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="19">
         <f>'1. Assumptions'!E15</f>
         <v>150000</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B10" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="22">
+      <c r="B10" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="17">
         <f>C8-C9</f>
         <v>268000</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="17">
         <f>D8-D9</f>
         <v>125000</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="17">
         <f>E8-E9</f>
         <v>-50000</v>
       </c>
-      <c r="F10" s="21"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B11" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="23">
+      <c r="B11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="18">
         <f>IFERROR(C10/C8,0)</f>
         <v>0.89333333333333331</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="18">
         <f>IFERROR(D10/D8,0)</f>
         <v>0.625</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="18">
         <f>IFERROR(E10/E8,0)</f>
         <v>-0.5</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="16"/>
+      <c r="G11" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B13" s="51" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="25">
+      <c r="C14" s="20">
         <f>'1. Assumptions'!C19</f>
         <v>100</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="20">
         <f>'1. Assumptions'!D19</f>
         <v>50</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="20">
         <f>'1. Assumptions'!E19</f>
         <v>20</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B15" s="14" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B15" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="22">
+      <c r="C15" s="17">
         <f>C10*C14</f>
         <v>26800000</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="17">
         <f>D10*D14</f>
         <v>6250000</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="17">
         <f>E10*E14</f>
         <v>-1000000</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="6" t="s">
+      <c r="F15" s="16"/>
+      <c r="G15" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B17" s="51" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B18" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="24">
+      <c r="C18" s="19">
         <f>'1. Assumptions'!C22</f>
         <v>50000</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="19">
         <f>'1. Assumptions'!D22</f>
         <v>100000</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="19">
         <f>'1. Assumptions'!E22</f>
         <v>200000</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B21" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B21" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="26">
+      <c r="C21" s="21">
         <f>IFERROR(C15/C18,0)</f>
         <v>536</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="21">
         <f>IFERROR(D15/D18,0)</f>
         <v>62.5</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="21">
         <f>IFERROR(E15/E18,0)</f>
         <v>-5</v>
       </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="6" t="s">
+      <c r="F21" s="16"/>
+      <c r="G21" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B22" s="14" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B22" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="20">
+      <c r="C22" s="15">
         <f>IFERROR(C18/C10,0)</f>
         <v>0.18656716417910449</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="15">
         <f>IFERROR(D18/D10,0)</f>
         <v>0.8</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="15">
         <f>IFERROR(E18/E10,0)</f>
         <v>-4</v>
       </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="6" t="s">
+      <c r="F22" s="16"/>
+      <c r="G22" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B24" s="51" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B25" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B25" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="27" t="str">
+      <c r="C25" s="22" t="str">
         <f>IF(AND(C21&gt;=3,C22&lt;=12),"✓ HEALTHY",IF(OR(C21&lt;1,C22&gt;18),"✗ UNHEALTHY","⚠ WATCH"))</f>
         <v>✓ HEALTHY</v>
       </c>
-      <c r="D25" s="27" t="str">
+      <c r="D25" s="22" t="str">
         <f>IF(AND(D21&gt;=3,D22&lt;=12),"✓ HEALTHY",IF(OR(D21&lt;1,D22&gt;18),"✗ UNHEALTHY","⚠ WATCH"))</f>
         <v>✓ HEALTHY</v>
       </c>
-      <c r="E25" s="27" t="str">
+      <c r="E25" s="22" t="str">
         <f>IF(AND(E21&gt;=3,E22&lt;=12),"✓ HEALTHY",IF(OR(E21&lt;1,E22&gt;18),"✗ UNHEALTHY","⚠ WATCH"))</f>
         <v>✗ UNHEALTHY</v>
       </c>
@@ -2121,1481 +2121,1481 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+    </row>
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="28" t="s">
+      <c r="C4" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B6" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <f>MATCH(C4,{"Optimistic","Base","Pessimistic"},0)</f>
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B8" s="27" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="33">
+      <c r="C8" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C7,'1. Assumptions'!D7,'1. Assumptions'!E7)</f>
         <v>200000</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B9" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="34">
+      <c r="B9" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="29">
         <f>CHOOSE($C$6,'1. Assumptions'!C8,'1. Assumptions'!D8,'1. Assumptions'!E8)</f>
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B10" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="33">
+      <c r="B10" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C9,'1. Assumptions'!D9,'1. Assumptions'!E9)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B11" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="33">
+      <c r="B11" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C15,'1. Assumptions'!D15,'1. Assumptions'!E15)</f>
         <v>75000</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="34">
+      <c r="B12" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="29">
         <f>CHOOSE($C$6,'1. Assumptions'!C18,'1. Assumptions'!D18,'1. Assumptions'!E18)</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B13" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="33">
+      <c r="B13" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C22,'1. Assumptions'!D22,'1. Assumptions'!E22)</f>
         <v>100000</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="33">
+      <c r="B14" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C28,'1. Assumptions'!D28,'1. Assumptions'!E28)</f>
         <v>145000000</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="33">
+      <c r="B15" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C31,'1. Assumptions'!D31,'1. Assumptions'!E31)</f>
         <v>300000000</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="33">
+      <c r="B16" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C32,'1. Assumptions'!D32,'1. Assumptions'!E32)</f>
         <v>2000000000</v>
       </c>
     </row>
     <row r="17" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B17" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="34">
+      <c r="B17" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="29">
         <f>CHOOSE($C$6,'1. Assumptions'!C36,'1. Assumptions'!D36,'1. Assumptions'!E36)</f>
         <v>1.5309470499731193E-2</v>
       </c>
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="51"/>
+      <c r="R20" s="51"/>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="51"/>
+      <c r="V20" s="51"/>
+      <c r="W20" s="51"/>
+      <c r="X20" s="51"/>
+      <c r="Y20" s="51"/>
+      <c r="Z20" s="51"/>
+      <c r="AA20" s="51"/>
+    </row>
+    <row r="21" spans="2:27" x14ac:dyDescent="0.45">
+      <c r="B21" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
-    </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B21" s="35" t="s">
+      <c r="C21" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="D21" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="E21" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="F21" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="G21" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="H21" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="H21" s="36" t="s">
+      <c r="I21" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="I21" s="36" t="s">
+      <c r="J21" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="K21" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="K21" s="36" t="s">
+      <c r="L21" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="L21" s="36" t="s">
+      <c r="M21" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="M21" s="36" t="s">
+      <c r="N21" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="N21" s="36" t="s">
+      <c r="O21" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="O21" s="36" t="s">
+      <c r="P21" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="P21" s="36" t="s">
+      <c r="Q21" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="Q21" s="36" t="s">
+      <c r="R21" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="R21" s="36" t="s">
+      <c r="S21" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="S21" s="36" t="s">
+      <c r="T21" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="T21" s="36" t="s">
+      <c r="U21" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="U21" s="36" t="s">
+      <c r="V21" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="V21" s="36" t="s">
+      <c r="W21" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="W21" s="36" t="s">
+      <c r="X21" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="X21" s="36" t="s">
+      <c r="Y21" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="Y21" s="36" t="s">
+      <c r="Z21" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="Z21" s="36" t="s">
+      <c r="AA21" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="AA21" s="37" t="s">
+    </row>
+    <row r="22" spans="2:27" x14ac:dyDescent="0.45">
+      <c r="B22" s="7" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B22" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="38">
+      <c r="C22" s="33">
         <f t="shared" ref="C22:Z22" si="0">ROUND($C$10*$C$9,0)</f>
         <v>250</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="K22" s="38">
+      <c r="K22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="L22" s="38">
+      <c r="L22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="M22" s="38">
+      <c r="M22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="N22" s="38">
+      <c r="N22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="O22" s="38">
+      <c r="O22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="P22" s="38">
+      <c r="P22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="Q22" s="38">
+      <c r="Q22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="R22" s="38">
+      <c r="R22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="S22" s="38">
+      <c r="S22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="T22" s="38">
+      <c r="T22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="U22" s="38">
+      <c r="U22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="V22" s="38">
+      <c r="V22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="W22" s="38">
+      <c r="W22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="X22" s="38">
+      <c r="X22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="Y22" s="38">
+      <c r="Y22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="Z22" s="38">
+      <c r="Z22" s="33">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="AA22" s="39">
+      <c r="AA22" s="34">
         <f>SUM(C22:Z22)</f>
         <v>6000</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B23" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="38">
+      <c r="B23" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="33">
         <f>C22</f>
         <v>250</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="33">
         <f t="shared" ref="D23:Z23" si="1">C23*(1-$C$12)+D22</f>
         <v>495</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E23" s="33">
         <f t="shared" si="1"/>
         <v>735.09999999999991</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="33">
         <f t="shared" si="1"/>
         <v>970.39799999999991</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23" s="33">
         <f t="shared" si="1"/>
         <v>1200.9900399999999</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23" s="33">
         <f t="shared" si="1"/>
         <v>1426.9702391999999</v>
       </c>
-      <c r="I23" s="38">
+      <c r="I23" s="33">
         <f t="shared" si="1"/>
         <v>1648.4308344159999</v>
       </c>
-      <c r="J23" s="38">
+      <c r="J23" s="33">
         <f t="shared" si="1"/>
         <v>1865.4622177276799</v>
       </c>
-      <c r="K23" s="38">
+      <c r="K23" s="33">
         <f t="shared" si="1"/>
         <v>2078.1529733731263</v>
       </c>
-      <c r="L23" s="38">
+      <c r="L23" s="33">
         <f t="shared" si="1"/>
         <v>2286.5899139056637</v>
       </c>
-      <c r="M23" s="38">
+      <c r="M23" s="33">
         <f t="shared" si="1"/>
         <v>2490.8581156275504</v>
       </c>
-      <c r="N23" s="38">
+      <c r="N23" s="33">
         <f t="shared" si="1"/>
         <v>2691.0409533149996</v>
       </c>
-      <c r="O23" s="38">
+      <c r="O23" s="33">
         <f t="shared" si="1"/>
         <v>2887.2201342486997</v>
       </c>
-      <c r="P23" s="38">
+      <c r="P23" s="33">
         <f t="shared" si="1"/>
         <v>3079.4757315637257</v>
       </c>
-      <c r="Q23" s="38">
+      <c r="Q23" s="33">
         <f t="shared" si="1"/>
         <v>3267.8862169324511</v>
       </c>
-      <c r="R23" s="38">
+      <c r="R23" s="33">
         <f t="shared" si="1"/>
         <v>3452.5284925938022</v>
       </c>
-      <c r="S23" s="38">
+      <c r="S23" s="33">
         <f t="shared" si="1"/>
         <v>3633.4779227419262</v>
       </c>
-      <c r="T23" s="38">
+      <c r="T23" s="33">
         <f t="shared" si="1"/>
         <v>3810.8083642870874</v>
       </c>
-      <c r="U23" s="38">
+      <c r="U23" s="33">
         <f t="shared" si="1"/>
         <v>3984.5921970013455</v>
       </c>
-      <c r="V23" s="38">
+      <c r="V23" s="33">
         <f t="shared" si="1"/>
         <v>4154.900353061319</v>
       </c>
-      <c r="W23" s="38">
+      <c r="W23" s="33">
         <f t="shared" si="1"/>
         <v>4321.8023460000932</v>
       </c>
-      <c r="X23" s="38">
+      <c r="X23" s="33">
         <f t="shared" si="1"/>
         <v>4485.3662990800913</v>
       </c>
-      <c r="Y23" s="38">
+      <c r="Y23" s="33">
         <f t="shared" si="1"/>
         <v>4645.6589730984897</v>
       </c>
-      <c r="Z23" s="38">
+      <c r="Z23" s="33">
         <f t="shared" si="1"/>
         <v>4802.7457936365199</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B25" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="41">
+      <c r="B25" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="36">
         <f t="shared" ref="C25:Z25" si="2">C23*$C$8</f>
         <v>50000000</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="36">
         <f t="shared" si="2"/>
         <v>99000000</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="36">
         <f t="shared" si="2"/>
         <v>147019999.99999997</v>
       </c>
-      <c r="F25" s="41">
+      <c r="F25" s="36">
         <f t="shared" si="2"/>
         <v>194079599.99999997</v>
       </c>
-      <c r="G25" s="41">
+      <c r="G25" s="36">
         <f t="shared" si="2"/>
         <v>240198007.99999997</v>
       </c>
-      <c r="H25" s="41">
+      <c r="H25" s="36">
         <f t="shared" si="2"/>
         <v>285394047.83999997</v>
       </c>
-      <c r="I25" s="41">
+      <c r="I25" s="36">
         <f t="shared" si="2"/>
         <v>329686166.88319999</v>
       </c>
-      <c r="J25" s="41">
+      <c r="J25" s="36">
         <f t="shared" si="2"/>
         <v>373092443.54553598</v>
       </c>
-      <c r="K25" s="41">
+      <c r="K25" s="36">
         <f t="shared" si="2"/>
         <v>415630594.67462528</v>
       </c>
-      <c r="L25" s="41">
+      <c r="L25" s="36">
         <f t="shared" si="2"/>
         <v>457317982.78113276</v>
       </c>
-      <c r="M25" s="41">
+      <c r="M25" s="36">
         <f t="shared" si="2"/>
         <v>498171623.1255101</v>
       </c>
-      <c r="N25" s="41">
+      <c r="N25" s="36">
         <f t="shared" si="2"/>
         <v>538208190.66299987</v>
       </c>
-      <c r="O25" s="41">
+      <c r="O25" s="36">
         <f t="shared" si="2"/>
         <v>577444026.84973991</v>
       </c>
-      <c r="P25" s="41">
+      <c r="P25" s="36">
         <f t="shared" si="2"/>
         <v>615895146.31274509</v>
       </c>
-      <c r="Q25" s="41">
+      <c r="Q25" s="36">
         <f t="shared" si="2"/>
         <v>653577243.38649023</v>
       </c>
-      <c r="R25" s="41">
+      <c r="R25" s="36">
         <f t="shared" si="2"/>
         <v>690505698.51876044</v>
       </c>
-      <c r="S25" s="41">
+      <c r="S25" s="36">
         <f t="shared" si="2"/>
         <v>726695584.54838526</v>
       </c>
-      <c r="T25" s="41">
+      <c r="T25" s="36">
         <f t="shared" si="2"/>
         <v>762161672.85741746</v>
       </c>
-      <c r="U25" s="41">
+      <c r="U25" s="36">
         <f t="shared" si="2"/>
         <v>796918439.40026915</v>
       </c>
-      <c r="V25" s="41">
+      <c r="V25" s="36">
         <f t="shared" si="2"/>
         <v>830980070.6122638</v>
       </c>
-      <c r="W25" s="41">
+      <c r="W25" s="36">
         <f t="shared" si="2"/>
         <v>864360469.20001864</v>
       </c>
-      <c r="X25" s="41">
+      <c r="X25" s="36">
         <f t="shared" si="2"/>
         <v>897073259.81601822</v>
       </c>
-      <c r="Y25" s="41">
+      <c r="Y25" s="36">
         <f t="shared" si="2"/>
         <v>929131794.61969793</v>
       </c>
-      <c r="Z25" s="41">
+      <c r="Z25" s="36">
         <f t="shared" si="2"/>
         <v>960549158.72730398</v>
       </c>
-      <c r="AA25" s="42">
+      <c r="AA25" s="37">
         <f t="shared" ref="AA25:AA30" si="3">SUM(C25:Z25)</f>
         <v>12933091222.362116</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B26" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" s="38">
+      <c r="B26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="33">
         <f t="shared" ref="C26:Z26" si="4">C23*$C$11</f>
         <v>18750000</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="33">
         <f t="shared" si="4"/>
         <v>37125000</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="33">
         <f t="shared" si="4"/>
         <v>55132499.999999993</v>
       </c>
-      <c r="F26" s="38">
+      <c r="F26" s="33">
         <f t="shared" si="4"/>
         <v>72779850</v>
       </c>
-      <c r="G26" s="38">
+      <c r="G26" s="33">
         <f t="shared" si="4"/>
         <v>90074253</v>
       </c>
-      <c r="H26" s="38">
+      <c r="H26" s="33">
         <f t="shared" si="4"/>
         <v>107022767.94</v>
       </c>
-      <c r="I26" s="38">
+      <c r="I26" s="33">
         <f t="shared" si="4"/>
         <v>123632312.58119999</v>
       </c>
-      <c r="J26" s="38">
+      <c r="J26" s="33">
         <f t="shared" si="4"/>
         <v>139909666.32957599</v>
       </c>
-      <c r="K26" s="38">
+      <c r="K26" s="33">
         <f t="shared" si="4"/>
         <v>155861473.00298446</v>
       </c>
-      <c r="L26" s="38">
+      <c r="L26" s="33">
         <f t="shared" si="4"/>
         <v>171494243.54292479</v>
       </c>
-      <c r="M26" s="38">
+      <c r="M26" s="33">
         <f t="shared" si="4"/>
         <v>186814358.67206627</v>
       </c>
-      <c r="N26" s="38">
+      <c r="N26" s="33">
         <f t="shared" si="4"/>
         <v>201828071.49862498</v>
       </c>
-      <c r="O26" s="38">
+      <c r="O26" s="33">
         <f t="shared" si="4"/>
         <v>216541510.06865248</v>
       </c>
-      <c r="P26" s="38">
+      <c r="P26" s="33">
         <f t="shared" si="4"/>
         <v>230960679.86727944</v>
       </c>
-      <c r="Q26" s="38">
+      <c r="Q26" s="33">
         <f t="shared" si="4"/>
         <v>245091466.26993385</v>
       </c>
-      <c r="R26" s="38">
+      <c r="R26" s="33">
         <f t="shared" si="4"/>
         <v>258939636.94453517</v>
       </c>
-      <c r="S26" s="38">
+      <c r="S26" s="33">
         <f t="shared" si="4"/>
         <v>272510844.20564449</v>
       </c>
-      <c r="T26" s="38">
+      <c r="T26" s="33">
         <f t="shared" si="4"/>
         <v>285810627.32153153</v>
       </c>
-      <c r="U26" s="38">
+      <c r="U26" s="33">
         <f t="shared" si="4"/>
         <v>298844414.77510089</v>
       </c>
-      <c r="V26" s="38">
+      <c r="V26" s="33">
         <f t="shared" si="4"/>
         <v>311617526.47959894</v>
       </c>
-      <c r="W26" s="38">
+      <c r="W26" s="33">
         <f t="shared" si="4"/>
         <v>324135175.95000696</v>
       </c>
-      <c r="X26" s="38">
+      <c r="X26" s="33">
         <f t="shared" si="4"/>
         <v>336402472.43100685</v>
       </c>
-      <c r="Y26" s="38">
+      <c r="Y26" s="33">
         <f t="shared" si="4"/>
         <v>348424422.98238671</v>
       </c>
-      <c r="Z26" s="38">
+      <c r="Z26" s="33">
         <f t="shared" si="4"/>
         <v>360205934.52273899</v>
       </c>
-      <c r="AA26" s="39">
+      <c r="AA26" s="34">
         <f t="shared" si="3"/>
         <v>4849909208.3857937</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B27" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" s="43">
+      <c r="B27" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="38">
         <f t="shared" ref="C27:Z27" si="5">C25-C26</f>
         <v>31250000</v>
       </c>
-      <c r="D27" s="43">
+      <c r="D27" s="38">
         <f t="shared" si="5"/>
         <v>61875000</v>
       </c>
-      <c r="E27" s="43">
+      <c r="E27" s="38">
         <f t="shared" si="5"/>
         <v>91887499.99999997</v>
       </c>
-      <c r="F27" s="43">
+      <c r="F27" s="38">
         <f t="shared" si="5"/>
         <v>121299749.99999997</v>
       </c>
-      <c r="G27" s="43">
+      <c r="G27" s="38">
         <f t="shared" si="5"/>
         <v>150123754.99999997</v>
       </c>
-      <c r="H27" s="43">
+      <c r="H27" s="38">
         <f t="shared" si="5"/>
         <v>178371279.89999998</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="38">
         <f t="shared" si="5"/>
         <v>206053854.30199999</v>
       </c>
-      <c r="J27" s="43">
+      <c r="J27" s="38">
         <f t="shared" si="5"/>
         <v>233182777.21596</v>
       </c>
-      <c r="K27" s="43">
+      <c r="K27" s="38">
         <f t="shared" si="5"/>
         <v>259769121.67164081</v>
       </c>
-      <c r="L27" s="43">
+      <c r="L27" s="38">
         <f t="shared" si="5"/>
         <v>285823739.23820794</v>
       </c>
-      <c r="M27" s="43">
+      <c r="M27" s="38">
         <f t="shared" si="5"/>
         <v>311357264.45344383</v>
       </c>
-      <c r="N27" s="43">
+      <c r="N27" s="38">
         <f t="shared" si="5"/>
         <v>336380119.16437489</v>
       </c>
-      <c r="O27" s="43">
+      <c r="O27" s="38">
         <f t="shared" si="5"/>
         <v>360902516.7810874</v>
       </c>
-      <c r="P27" s="43">
+      <c r="P27" s="38">
         <f t="shared" si="5"/>
         <v>384934466.44546568</v>
       </c>
-      <c r="Q27" s="43">
+      <c r="Q27" s="38">
         <f t="shared" si="5"/>
         <v>408485777.11655641</v>
       </c>
-      <c r="R27" s="43">
+      <c r="R27" s="38">
         <f t="shared" si="5"/>
         <v>431566061.57422531</v>
       </c>
-      <c r="S27" s="43">
+      <c r="S27" s="38">
         <f t="shared" si="5"/>
         <v>454184740.34274077</v>
       </c>
-      <c r="T27" s="43">
+      <c r="T27" s="38">
         <f t="shared" si="5"/>
         <v>476351045.53588593</v>
       </c>
-      <c r="U27" s="43">
+      <c r="U27" s="38">
         <f t="shared" si="5"/>
         <v>498074024.62516826</v>
       </c>
-      <c r="V27" s="43">
+      <c r="V27" s="38">
         <f t="shared" si="5"/>
         <v>519362544.13266486</v>
       </c>
-      <c r="W27" s="43">
+      <c r="W27" s="38">
         <f t="shared" si="5"/>
         <v>540225293.25001168</v>
       </c>
-      <c r="X27" s="43">
+      <c r="X27" s="38">
         <f t="shared" si="5"/>
         <v>560670787.38501143</v>
       </c>
-      <c r="Y27" s="43">
+      <c r="Y27" s="38">
         <f t="shared" si="5"/>
         <v>580707371.63731122</v>
       </c>
-      <c r="Z27" s="43">
+      <c r="Z27" s="38">
         <f t="shared" si="5"/>
         <v>600343224.20456505</v>
       </c>
-      <c r="AA27" s="39">
+      <c r="AA27" s="34">
         <f t="shared" si="3"/>
         <v>8083182013.9763212</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B28" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="38">
+      <c r="B28" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="33">
         <f t="shared" ref="C28:Z28" si="6">C22*$C$13</f>
         <v>25000000</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="F28" s="38">
+      <c r="F28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="G28" s="38">
+      <c r="G28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="I28" s="38">
+      <c r="I28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="L28" s="38">
+      <c r="L28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="M28" s="38">
+      <c r="M28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="N28" s="38">
+      <c r="N28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="O28" s="38">
+      <c r="O28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="P28" s="38">
+      <c r="P28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="Q28" s="38">
+      <c r="Q28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="R28" s="38">
+      <c r="R28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="S28" s="38">
+      <c r="S28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="T28" s="38">
+      <c r="T28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="U28" s="38">
+      <c r="U28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="V28" s="38">
+      <c r="V28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="W28" s="38">
+      <c r="W28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="X28" s="38">
+      <c r="X28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="Y28" s="38">
+      <c r="Y28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="Z28" s="38">
+      <c r="Z28" s="33">
         <f t="shared" si="6"/>
         <v>25000000</v>
       </c>
-      <c r="AA28" s="39">
+      <c r="AA28" s="34">
         <f t="shared" si="3"/>
         <v>600000000</v>
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B29" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29" s="38">
+      <c r="B29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="33">
         <f t="shared" ref="C29:Z29" si="7">$C$14</f>
         <v>145000000</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="E29" s="38">
+      <c r="E29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="F29" s="38">
+      <c r="F29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="G29" s="38">
+      <c r="G29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="H29" s="38">
+      <c r="H29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="I29" s="38">
+      <c r="I29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="J29" s="38">
+      <c r="J29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="K29" s="38">
+      <c r="K29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="L29" s="38">
+      <c r="L29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="M29" s="38">
+      <c r="M29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="N29" s="38">
+      <c r="N29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="O29" s="38">
+      <c r="O29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="P29" s="38">
+      <c r="P29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="Q29" s="38">
+      <c r="Q29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="R29" s="38">
+      <c r="R29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="S29" s="38">
+      <c r="S29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="T29" s="38">
+      <c r="T29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="U29" s="38">
+      <c r="U29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="V29" s="38">
+      <c r="V29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="W29" s="38">
+      <c r="W29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="X29" s="38">
+      <c r="X29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="Y29" s="38">
+      <c r="Y29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="Z29" s="38">
+      <c r="Z29" s="33">
         <f t="shared" si="7"/>
         <v>145000000</v>
       </c>
-      <c r="AA29" s="39">
+      <c r="AA29" s="34">
         <f t="shared" si="3"/>
         <v>3480000000</v>
       </c>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B30" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30" s="44">
+      <c r="B30" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="39">
         <f t="shared" ref="C30:Z30" si="8">C27-C28-C29</f>
         <v>-138750000</v>
       </c>
-      <c r="D30" s="44">
+      <c r="D30" s="39">
         <f t="shared" si="8"/>
         <v>-108125000</v>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="39">
         <f t="shared" si="8"/>
         <v>-78112500.00000003</v>
       </c>
-      <c r="F30" s="44">
+      <c r="F30" s="39">
         <f t="shared" si="8"/>
         <v>-48700250.00000003</v>
       </c>
-      <c r="G30" s="44">
+      <c r="G30" s="39">
         <f t="shared" si="8"/>
         <v>-19876245.00000003</v>
       </c>
-      <c r="H30" s="44">
+      <c r="H30" s="39">
         <f t="shared" si="8"/>
         <v>8371279.8999999762</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="39">
         <f t="shared" si="8"/>
         <v>36053854.301999986</v>
       </c>
-      <c r="J30" s="44">
+      <c r="J30" s="39">
         <f t="shared" si="8"/>
         <v>63182777.215959996</v>
       </c>
-      <c r="K30" s="44">
+      <c r="K30" s="39">
         <f t="shared" si="8"/>
         <v>89769121.671640813</v>
       </c>
-      <c r="L30" s="44">
+      <c r="L30" s="39">
         <f t="shared" si="8"/>
         <v>115823739.23820794</v>
       </c>
-      <c r="M30" s="44">
+      <c r="M30" s="39">
         <f t="shared" si="8"/>
         <v>141357264.45344383</v>
       </c>
-      <c r="N30" s="44">
+      <c r="N30" s="39">
         <f t="shared" si="8"/>
         <v>166380119.16437489</v>
       </c>
-      <c r="O30" s="44">
+      <c r="O30" s="39">
         <f t="shared" si="8"/>
         <v>190902516.7810874</v>
       </c>
-      <c r="P30" s="44">
+      <c r="P30" s="39">
         <f t="shared" si="8"/>
         <v>214934466.44546568</v>
       </c>
-      <c r="Q30" s="44">
+      <c r="Q30" s="39">
         <f t="shared" si="8"/>
         <v>238485777.11655641</v>
       </c>
-      <c r="R30" s="44">
+      <c r="R30" s="39">
         <f t="shared" si="8"/>
         <v>261566061.57422531</v>
       </c>
-      <c r="S30" s="44">
+      <c r="S30" s="39">
         <f t="shared" si="8"/>
         <v>284184740.34274077</v>
       </c>
-      <c r="T30" s="44">
+      <c r="T30" s="39">
         <f t="shared" si="8"/>
         <v>306351045.53588593</v>
       </c>
-      <c r="U30" s="44">
+      <c r="U30" s="39">
         <f t="shared" si="8"/>
         <v>328074024.62516826</v>
       </c>
-      <c r="V30" s="44">
+      <c r="V30" s="39">
         <f t="shared" si="8"/>
         <v>349362544.13266486</v>
       </c>
-      <c r="W30" s="44">
+      <c r="W30" s="39">
         <f t="shared" si="8"/>
         <v>370225293.25001168</v>
       </c>
-      <c r="X30" s="44">
+      <c r="X30" s="39">
         <f t="shared" si="8"/>
         <v>390670787.38501143</v>
       </c>
-      <c r="Y30" s="44">
+      <c r="Y30" s="39">
         <f t="shared" si="8"/>
         <v>410707371.63731122</v>
       </c>
-      <c r="Z30" s="44">
+      <c r="Z30" s="39">
         <f t="shared" si="8"/>
         <v>430343224.20456505</v>
       </c>
-      <c r="AA30" s="45">
+      <c r="AA30" s="40">
         <f t="shared" si="3"/>
         <v>4003182013.9763212</v>
       </c>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.45">
-      <c r="B32" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C32" s="38">
+      <c r="B32" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="33">
         <f>C30-$C$15</f>
         <v>-438750000</v>
       </c>
-      <c r="D32" s="38">
+      <c r="D32" s="33">
         <f t="shared" ref="D32:Z32" si="9">D30</f>
         <v>-108125000</v>
       </c>
-      <c r="E32" s="38">
+      <c r="E32" s="33">
         <f t="shared" si="9"/>
         <v>-78112500.00000003</v>
       </c>
-      <c r="F32" s="38">
+      <c r="F32" s="33">
         <f t="shared" si="9"/>
         <v>-48700250.00000003</v>
       </c>
-      <c r="G32" s="38">
+      <c r="G32" s="33">
         <f t="shared" si="9"/>
         <v>-19876245.00000003</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32" s="33">
         <f t="shared" si="9"/>
         <v>8371279.8999999762</v>
       </c>
-      <c r="I32" s="38">
+      <c r="I32" s="33">
         <f t="shared" si="9"/>
         <v>36053854.301999986</v>
       </c>
-      <c r="J32" s="38">
+      <c r="J32" s="33">
         <f t="shared" si="9"/>
         <v>63182777.215959996</v>
       </c>
-      <c r="K32" s="38">
+      <c r="K32" s="33">
         <f t="shared" si="9"/>
         <v>89769121.671640813</v>
       </c>
-      <c r="L32" s="38">
+      <c r="L32" s="33">
         <f t="shared" si="9"/>
         <v>115823739.23820794</v>
       </c>
-      <c r="M32" s="38">
+      <c r="M32" s="33">
         <f t="shared" si="9"/>
         <v>141357264.45344383</v>
       </c>
-      <c r="N32" s="38">
+      <c r="N32" s="33">
         <f t="shared" si="9"/>
         <v>166380119.16437489</v>
       </c>
-      <c r="O32" s="38">
+      <c r="O32" s="33">
         <f t="shared" si="9"/>
         <v>190902516.7810874</v>
       </c>
-      <c r="P32" s="38">
+      <c r="P32" s="33">
         <f t="shared" si="9"/>
         <v>214934466.44546568</v>
       </c>
-      <c r="Q32" s="38">
+      <c r="Q32" s="33">
         <f t="shared" si="9"/>
         <v>238485777.11655641</v>
       </c>
-      <c r="R32" s="38">
+      <c r="R32" s="33">
         <f t="shared" si="9"/>
         <v>261566061.57422531</v>
       </c>
-      <c r="S32" s="38">
+      <c r="S32" s="33">
         <f t="shared" si="9"/>
         <v>284184740.34274077</v>
       </c>
-      <c r="T32" s="38">
+      <c r="T32" s="33">
         <f t="shared" si="9"/>
         <v>306351045.53588593</v>
       </c>
-      <c r="U32" s="38">
+      <c r="U32" s="33">
         <f t="shared" si="9"/>
         <v>328074024.62516826</v>
       </c>
-      <c r="V32" s="38">
+      <c r="V32" s="33">
         <f t="shared" si="9"/>
         <v>349362544.13266486</v>
       </c>
-      <c r="W32" s="38">
+      <c r="W32" s="33">
         <f t="shared" si="9"/>
         <v>370225293.25001168</v>
       </c>
-      <c r="X32" s="38">
+      <c r="X32" s="33">
         <f t="shared" si="9"/>
         <v>390670787.38501143</v>
       </c>
-      <c r="Y32" s="38">
+      <c r="Y32" s="33">
         <f t="shared" si="9"/>
         <v>410707371.63731122</v>
       </c>
-      <c r="Z32" s="38">
+      <c r="Z32" s="33">
         <f t="shared" si="9"/>
         <v>430343224.20456505</v>
       </c>
-      <c r="AA32" s="39">
+      <c r="AA32" s="34">
         <f>SUM(C32:Z32)</f>
         <v>3703182013.9763212</v>
       </c>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="B33" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="C33" s="47">
+      <c r="B33" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="42">
         <f>$C$16+C32</f>
         <v>1561250000</v>
       </c>
-      <c r="D33" s="47">
+      <c r="D33" s="42">
         <f t="shared" ref="D33:Z33" si="10">C33+D32</f>
         <v>1453125000</v>
       </c>
-      <c r="E33" s="47">
+      <c r="E33" s="42">
         <f t="shared" si="10"/>
         <v>1375012500</v>
       </c>
-      <c r="F33" s="47">
+      <c r="F33" s="42">
         <f t="shared" si="10"/>
         <v>1326312250</v>
       </c>
-      <c r="G33" s="47">
+      <c r="G33" s="42">
         <f t="shared" si="10"/>
         <v>1306436005</v>
       </c>
-      <c r="H33" s="47">
+      <c r="H33" s="42">
         <f t="shared" si="10"/>
         <v>1314807284.9000001</v>
       </c>
-      <c r="I33" s="47">
+      <c r="I33" s="42">
         <f t="shared" si="10"/>
         <v>1350861139.2020001</v>
       </c>
-      <c r="J33" s="47">
+      <c r="J33" s="42">
         <f t="shared" si="10"/>
         <v>1414043916.4179602</v>
       </c>
-      <c r="K33" s="47">
+      <c r="K33" s="42">
         <f t="shared" si="10"/>
         <v>1503813038.089601</v>
       </c>
-      <c r="L33" s="47">
+      <c r="L33" s="42">
         <f t="shared" si="10"/>
         <v>1619636777.3278089</v>
       </c>
-      <c r="M33" s="47">
+      <c r="M33" s="42">
         <f t="shared" si="10"/>
         <v>1760994041.7812526</v>
       </c>
-      <c r="N33" s="47">
+      <c r="N33" s="42">
         <f t="shared" si="10"/>
         <v>1927374160.9456275</v>
       </c>
-      <c r="O33" s="47">
+      <c r="O33" s="42">
         <f t="shared" si="10"/>
         <v>2118276677.7267148</v>
       </c>
-      <c r="P33" s="47">
+      <c r="P33" s="42">
         <f t="shared" si="10"/>
         <v>2333211144.1721807</v>
       </c>
-      <c r="Q33" s="47">
+      <c r="Q33" s="42">
         <f t="shared" si="10"/>
         <v>2571696921.2887373</v>
       </c>
-      <c r="R33" s="47">
+      <c r="R33" s="42">
         <f t="shared" si="10"/>
         <v>2833262982.8629627</v>
       </c>
-      <c r="S33" s="47">
+      <c r="S33" s="42">
         <f t="shared" si="10"/>
         <v>3117447723.2057037</v>
       </c>
-      <c r="T33" s="47">
+      <c r="T33" s="42">
         <f t="shared" si="10"/>
         <v>3423798768.7415895</v>
       </c>
-      <c r="U33" s="47">
+      <c r="U33" s="42">
         <f t="shared" si="10"/>
         <v>3751872793.3667579</v>
       </c>
-      <c r="V33" s="47">
+      <c r="V33" s="42">
         <f t="shared" si="10"/>
         <v>4101235337.4994226</v>
       </c>
-      <c r="W33" s="47">
+      <c r="W33" s="42">
         <f t="shared" si="10"/>
         <v>4471460630.7494345</v>
       </c>
-      <c r="X33" s="47">
+      <c r="X33" s="42">
         <f t="shared" si="10"/>
         <v>4862131418.1344461</v>
       </c>
-      <c r="Y33" s="47">
+      <c r="Y33" s="42">
         <f t="shared" si="10"/>
         <v>5272838789.7717571</v>
       </c>
-      <c r="Z33" s="47">
+      <c r="Z33" s="42">
         <f t="shared" si="10"/>
         <v>5703182013.9763222</v>
       </c>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.45">
+      <c r="B37" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="B37" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C37" s="48">
+      <c r="C37" s="43">
         <f>(NPV($C$17,D32:Z32)+C32)/1000000</f>
         <v>2715.9020493737012</v>
       </c>
-      <c r="D37" s="30" t="str">
+      <c r="D37" s="25" t="str">
         <f>"(target: &gt; 0)"</f>
         <v>(target: &gt; 0)</v>
       </c>
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="B38" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" s="49">
+      <c r="B38" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="44">
         <f>IFERROR((1+IRR(C32:Z32))^12-1,0)</f>
         <v>3.3489801297866899</v>
       </c>
-      <c r="D38" s="30" t="str">
+      <c r="D38" s="25" t="str">
         <f>"(target: &gt; "&amp;TEXT(CHOOSE($C$6,'1. Assumptions'!C35,'1. Assumptions'!D35,'1. Assumptions'!E35),"0.0%")&amp;")"</f>
         <v>(target: &gt; 20.0%)</v>
       </c>
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="B39" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C39" s="50">
+      <c r="B39" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="45">
         <f>IFERROR(MATCH(TRUE(),INDEX(C41:Z41&gt;=0,0),0),"&gt; 24")</f>
         <v>13</v>
       </c>
-      <c r="D39" s="30" t="str">
+      <c r="D39" s="25" t="str">
         <f>"(target: &lt; 24)"</f>
         <v>(target: &lt; 24)</v>
       </c>
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="B40" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C40" s="50" t="str">
+      <c r="B40" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="45" t="str">
         <f>IFERROR(MATCH(TRUE(),INDEX(C33:Z33&lt;0,0),0)-1,"&gt;= 24")</f>
         <v>&gt;= 24</v>
       </c>
-      <c r="D40" s="30" t="str">
+      <c r="D40" s="25" t="str">
         <f>"(target: &gt;= 12)"</f>
         <v>(target: &gt;= 12)</v>
       </c>
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="B41" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="C41" s="52">
+      <c r="B41" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="47">
         <f>C32</f>
         <v>-438750000</v>
       </c>
-      <c r="D41" s="52">
+      <c r="D41" s="47">
         <f t="shared" ref="D41:Z41" si="11">C41+D32</f>
         <v>-546875000</v>
       </c>
-      <c r="E41" s="52">
+      <c r="E41" s="47">
         <f t="shared" si="11"/>
         <v>-624987500</v>
       </c>
-      <c r="F41" s="52">
+      <c r="F41" s="47">
         <f t="shared" si="11"/>
         <v>-673687750</v>
       </c>
-      <c r="G41" s="52">
+      <c r="G41" s="47">
         <f t="shared" si="11"/>
         <v>-693563995</v>
       </c>
-      <c r="H41" s="52">
+      <c r="H41" s="47">
         <f t="shared" si="11"/>
         <v>-685192715.10000002</v>
       </c>
-      <c r="I41" s="52">
+      <c r="I41" s="47">
         <f t="shared" si="11"/>
         <v>-649138860.7980001</v>
       </c>
-      <c r="J41" s="52">
+      <c r="J41" s="47">
         <f t="shared" si="11"/>
         <v>-585956083.58204007</v>
       </c>
-      <c r="K41" s="52">
+      <c r="K41" s="47">
         <f t="shared" si="11"/>
         <v>-496186961.91039926</v>
       </c>
-      <c r="L41" s="52">
+      <c r="L41" s="47">
         <f t="shared" si="11"/>
         <v>-380363222.67219132</v>
       </c>
-      <c r="M41" s="52">
+      <c r="M41" s="47">
         <f t="shared" si="11"/>
         <v>-239005958.2187475</v>
       </c>
-      <c r="N41" s="52">
+      <c r="N41" s="47">
         <f t="shared" si="11"/>
         <v>-72625839.054372609</v>
       </c>
-      <c r="O41" s="52">
+      <c r="O41" s="47">
         <f t="shared" si="11"/>
         <v>118276677.72671479</v>
       </c>
-      <c r="P41" s="52">
+      <c r="P41" s="47">
         <f t="shared" si="11"/>
         <v>333211144.17218047</v>
       </c>
-      <c r="Q41" s="52">
+      <c r="Q41" s="47">
         <f t="shared" si="11"/>
         <v>571696921.28873682</v>
       </c>
-      <c r="R41" s="52">
+      <c r="R41" s="47">
         <f t="shared" si="11"/>
         <v>833262982.86296213</v>
       </c>
-      <c r="S41" s="52">
+      <c r="S41" s="47">
         <f t="shared" si="11"/>
         <v>1117447723.2057028</v>
       </c>
-      <c r="T41" s="52">
+      <c r="T41" s="47">
         <f t="shared" si="11"/>
         <v>1423798768.7415886</v>
       </c>
-      <c r="U41" s="52">
+      <c r="U41" s="47">
         <f t="shared" si="11"/>
         <v>1751872793.3667569</v>
       </c>
-      <c r="V41" s="52">
+      <c r="V41" s="47">
         <f t="shared" si="11"/>
         <v>2101235337.4994218</v>
       </c>
-      <c r="W41" s="52">
+      <c r="W41" s="47">
         <f t="shared" si="11"/>
         <v>2471460630.7494335</v>
       </c>
-      <c r="X41" s="52">
+      <c r="X41" s="47">
         <f t="shared" si="11"/>
         <v>2862131418.1344452</v>
       </c>
-      <c r="Y41" s="52">
+      <c r="Y41" s="47">
         <f t="shared" si="11"/>
         <v>3272838789.7717562</v>
       </c>
-      <c r="Z41" s="52">
+      <c r="Z41" s="47">
         <f t="shared" si="11"/>
         <v>3703182013.9763212</v>
       </c>
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="51"/>
+    </row>
+    <row r="44" spans="2:26" ht="15" x14ac:dyDescent="0.45">
+      <c r="B44" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-    </row>
-    <row r="44" spans="2:26" ht="15" x14ac:dyDescent="0.45">
-      <c r="B44" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C44" s="1" t="str">
+      <c r="C44" s="48" t="str">
         <f>IF(AND(C37&gt;0,C38&gt;CHOOSE($C$6,'1. Assumptions'!C35,'1. Assumptions'!D35,'1. Assumptions'!E35)),"✓ GO — NPV+ và IRR &gt; WACC",IF(C37&lt;0,"✗ NO-GO — NPV âm: dự án không tạo giá trị","⚠ HOLD — IRR thấp hơn kỳ vọng, cần điều chỉnh"))</f>
         <v>✓ GO — NPV+ và IRR &gt; WACC</v>
       </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="6">
